--- a/Docs/Cronograma/Cronograma FinanzaViva.xlsx
+++ b/Docs/Cronograma/Cronograma FinanzaViva.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe\Desktop\FinanzaViva\Docs\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C242359F-7548-4C23-8DE6-551B844F829B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0570B6D-B03D-4DC2-A381-E8FE70F81246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -564,131 +564,131 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,81 +1011,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="32" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="38" t="s">
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="38" t="s">
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="4" t="s">
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="29" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="18" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1094,10 +1094,10 @@
       <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="21" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1109,7 +1109,7 @@
       <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="18" t="s">
         <v>12</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -1124,961 +1124,960 @@
       <c r="S3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="43" t="s">
+      <c r="T3" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
     </row>
     <row r="5" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
     </row>
     <row r="6" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
     </row>
     <row r="7" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
     </row>
     <row r="8" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
     </row>
     <row r="10" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
     </row>
     <row r="11" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
     </row>
     <row r="12" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
     </row>
     <row r="13" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
     </row>
     <row r="14" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
     </row>
     <row r="16" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
     </row>
     <row r="17" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="44"/>
+      <c r="B17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
     </row>
     <row r="18" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
     </row>
     <row r="19" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
     </row>
     <row r="20" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="44"/>
+      <c r="B20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
     </row>
     <row r="21" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
-      <c r="B21" s="22" t="s">
+      <c r="A21" s="44"/>
+      <c r="B21" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
     </row>
     <row r="22" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
     </row>
     <row r="23" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25"/>
-      <c r="B23" s="22" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
     </row>
     <row r="24" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25"/>
-      <c r="B24" s="24" t="s">
+      <c r="A24" s="40"/>
+      <c r="B24" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
     </row>
     <row r="25" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25"/>
-      <c r="B25" s="22" t="s">
+      <c r="A25" s="40"/>
+      <c r="B25" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
     </row>
     <row r="26" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25"/>
-      <c r="B26" s="24" t="s">
+      <c r="A26" s="40"/>
+      <c r="B26" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
     </row>
     <row r="27" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="40"/>
+      <c r="B27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
     </row>
     <row r="28" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="25"/>
-      <c r="B28" s="24" t="s">
+      <c r="A28" s="40"/>
+      <c r="B28" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
     </row>
     <row r="29" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
     </row>
     <row r="30" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="24" t="s">
+      <c r="A30" s="38"/>
+      <c r="B30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
     </row>
     <row r="31" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="22" t="s">
+      <c r="A31" s="38"/>
+      <c r="B31" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
     </row>
     <row r="32" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="24" t="s">
+      <c r="A32" s="38"/>
+      <c r="B32" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
     </row>
     <row r="33" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
     </row>
     <row r="34" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="24" t="s">
+      <c r="A34" s="36"/>
+      <c r="B34" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
     </row>
     <row r="35" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="22" t="s">
+      <c r="A35" s="36"/>
+      <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
     </row>
     <row r="36" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
     </row>
     <row r="37" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="22" t="s">
+      <c r="A37" s="34"/>
+      <c r="B37" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
     </row>
     <row r="38" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="24" t="s">
+      <c r="A38" s="34"/>
+      <c r="B38" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
     </row>
     <row r="39" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="44"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="24"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
@@ -2089,28 +2088,24 @@
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="T2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A36:A38"/>
     <mergeCell ref="A33:A35"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="A29:A32"/>
@@ -2121,7 +2116,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="T2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Docs/Cronograma/Cronograma FinanzaViva.xlsx
+++ b/Docs/Cronograma/Cronograma FinanzaViva.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe\Desktop\FinanzaViva\Docs\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0570B6D-B03D-4DC2-A381-E8FE70F81246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64739A48-8EE8-4230-B0F8-767AB4AA14F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma FinanzaViva" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -257,11 +268,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +290,12 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -364,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -376,19 +388,6 @@
       <left style="thin">
         <color rgb="FFB0C4CC"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB0C4CC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0C4CC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FFB0C4CC"/>
       </right>
@@ -416,17 +415,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
@@ -441,19 +429,6 @@
       <top/>
       <bottom style="thin">
         <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB0C4CC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0C4CC"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -475,21 +450,6 @@
         <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB0C4CC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0C4CC"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -517,9 +477,11 @@
         <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,24 +489,7 @@
       <left style="thin">
         <color rgb="FFB0C4CC"/>
       </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0C4CC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0C4CC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0C4CC"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FFB0C4CC"/>
       </top>
@@ -557,132 +502,98 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -691,6 +602,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,6 +933,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:T72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1011,81 +948,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="41" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="30" t="s">
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="30" t="s">
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="29" t="s">
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="40" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="13" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1094,10 +1031,10 @@
       <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="13" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1109,7 +1046,7 @@
       <c r="N3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="13" t="s">
         <v>12</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -1124,984 +1061,984 @@
       <c r="S3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="23" t="s">
+      <c r="T3" s="41" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
     </row>
     <row r="5" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
     </row>
     <row r="6" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="11" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="11" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
     </row>
     <row r="11" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
     </row>
     <row r="12" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
     </row>
     <row r="13" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
     </row>
     <row r="14" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
     </row>
     <row r="15" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="32"/>
+      <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
     </row>
     <row r="16" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
     </row>
     <row r="17" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="32"/>
+      <c r="B17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
     </row>
     <row r="18" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="32"/>
+      <c r="B18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
     </row>
     <row r="19" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="32"/>
+      <c r="B19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
     </row>
     <row r="20" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="44"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="32"/>
+      <c r="B20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
     </row>
     <row r="21" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44"/>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="32"/>
+      <c r="B21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
     </row>
     <row r="22" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
     </row>
     <row r="23" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="28"/>
+      <c r="B23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
     </row>
     <row r="24" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="28"/>
+      <c r="B24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
     </row>
     <row r="25" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
-      <c r="B25" s="13" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
     </row>
     <row r="26" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
-      <c r="B26" s="14" t="s">
+      <c r="A26" s="28"/>
+      <c r="B26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
     </row>
     <row r="27" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
-      <c r="B27" s="13" t="s">
+      <c r="A27" s="28"/>
+      <c r="B27" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
     </row>
     <row r="28" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
-      <c r="B28" s="14" t="s">
+      <c r="A28" s="28"/>
+      <c r="B28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
     </row>
     <row r="29" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
     </row>
     <row r="30" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="26"/>
+      <c r="B30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
     </row>
     <row r="31" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
-      <c r="B31" s="13" t="s">
+      <c r="A31" s="26"/>
+      <c r="B31" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
     </row>
     <row r="32" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="26"/>
+      <c r="B32" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
     </row>
     <row r="33" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
     </row>
     <row r="34" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="24"/>
+      <c r="B34" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
     </row>
     <row r="35" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="13" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
     </row>
     <row r="36" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
     </row>
     <row r="37" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34"/>
-      <c r="B37" s="13" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
     </row>
     <row r="38" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34"/>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
     </row>
     <row r="39" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="24"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="14"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2123,5 +2060,6 @@
     <mergeCell ref="A11:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="50" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/Cronograma/Cronograma FinanzaViva.xlsx
+++ b/Docs/Cronograma/Cronograma FinanzaViva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felipe\Desktop\FinanzaViva\Docs\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64739A48-8EE8-4230-B0F8-767AB4AA14F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBB2C63-B150-4493-8B75-B9E90CD28C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>Módulo Quizzes (preguntas, recompensas)</t>
   </si>
   <si>
-    <t>Módulo Simulador financiero (turnos, multijugador)</t>
-  </si>
-  <si>
     <t>Módulo Dashboard (resumen, estadísticas)</t>
   </si>
   <si>
@@ -149,20 +146,11 @@
     <t>Integración backend-frontend por módulo</t>
   </si>
   <si>
-    <t>Pruebas unitarias backend (Jest)</t>
-  </si>
-  <si>
-    <t>Pruebas E2E y flujos completos</t>
-  </si>
-  <si>
     <t>Corrección de bugs y refinamiento</t>
   </si>
   <si>
     <t>6. Documentación
 &amp; Despliegue</t>
-  </si>
-  <si>
-    <t>Documentación técnica (API, arquitectura)</t>
   </si>
   <si>
     <t>Manual de usuario y guía de instalación</t>
@@ -226,6 +214,18 @@
   </si>
   <si>
     <t>Felipe Molina</t>
+  </si>
+  <si>
+    <t>Módulo Simulador financiero (turnos, multijugador local)</t>
+  </si>
+  <si>
+    <t>Pruebas de flujos completos</t>
+  </si>
+  <si>
+    <t>Pruebas unitarias backend</t>
+  </si>
+  <si>
+    <t>Documentación técnica</t>
   </si>
 </sst>
 </file>
@@ -542,19 +542,81 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -563,68 +625,6 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -948,75 +948,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="29" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="18" t="s">
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="18" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="17" t="s">
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="39" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1031,7 +1031,7 @@
       <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K3" s="13" t="s">
@@ -1061,21 +1061,21 @@
       <c r="S3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="41" t="s">
+      <c r="T3" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
-        <v>49</v>
+      <c r="A4" s="43" t="s">
+        <v>45</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="42"/>
+      <c r="C4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="22"/>
       <c r="E4" s="12"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -1094,14 +1094,14 @@
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="42"/>
+      <c r="C5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="22"/>
       <c r="E5" s="12"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -1120,14 +1120,14 @@
       <c r="T5" s="6"/>
     </row>
     <row r="6" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="42"/>
+        <v>42</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="22"/>
       <c r="E6" s="12"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1146,14 +1146,14 @@
       <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="42"/>
+        <v>43</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="22"/>
       <c r="E7" s="6"/>
       <c r="F7" s="12"/>
       <c r="G7" s="6"/>
@@ -1172,14 +1172,14 @@
       <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="42"/>
+      <c r="C8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="22"/>
       <c r="E8" s="6"/>
       <c r="F8" s="12"/>
       <c r="G8" s="6"/>
@@ -1198,14 +1198,14 @@
       <c r="T8" s="6"/>
     </row>
     <row r="9" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="42"/>
+      <c r="C9" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="22"/>
       <c r="E9" s="6"/>
       <c r="F9" s="12"/>
       <c r="G9" s="6"/>
@@ -1224,14 +1224,14 @@
       <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="42"/>
+        <v>44</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="22"/>
       <c r="E10" s="6"/>
       <c r="F10" s="12"/>
       <c r="G10" s="6"/>
@@ -1250,21 +1250,21 @@
       <c r="T10" s="6"/>
     </row>
     <row r="11" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
-        <v>51</v>
+      <c r="A11" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="42"/>
+      <c r="J11" s="22"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1277,12 +1277,12 @@
       <c r="T11" s="6"/>
     </row>
     <row r="12" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>59</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="6"/>
@@ -1290,7 +1290,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="42"/>
+      <c r="J12" s="22"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1303,14 +1303,14 @@
       <c r="T12" s="6"/>
     </row>
     <row r="13" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="42"/>
+        <v>52</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="22"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -1329,16 +1329,16 @@
       <c r="T13" s="6"/>
     </row>
     <row r="14" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="42"/>
+      <c r="C14" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="22"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="12"/>
@@ -1357,14 +1357,14 @@
       <c r="T14" s="6"/>
     </row>
     <row r="15" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="42"/>
+      <c r="C15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="22"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="12"/>
@@ -1383,14 +1383,14 @@
       <c r="T15" s="6"/>
     </row>
     <row r="16" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="42"/>
+      <c r="C16" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="22"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="12"/>
@@ -1409,14 +1409,14 @@
       <c r="T16" s="6"/>
     </row>
     <row r="17" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="42"/>
+      <c r="C17" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="22"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -1435,14 +1435,14 @@
       <c r="T17" s="6"/>
     </row>
     <row r="18" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="42"/>
+      <c r="C18" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="22"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -1461,14 +1461,14 @@
       <c r="T18" s="6"/>
     </row>
     <row r="19" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="42"/>
+      <c r="C19" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="22"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1487,19 +1487,18 @@
       <c r="T19" s="6"/>
     </row>
     <row r="20" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="42"/>
+        <v>57</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="22"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="12"/>
+      <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
@@ -1513,14 +1512,14 @@
       <c r="T20" s="6"/>
     </row>
     <row r="21" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="42"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="22"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -1539,16 +1538,16 @@
       <c r="T21" s="6"/>
     </row>
     <row r="22" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="42"/>
+      <c r="C22" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="22"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1567,14 +1566,14 @@
       <c r="T22" s="6"/>
     </row>
     <row r="23" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="42"/>
+        <v>27</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="22"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -1593,14 +1592,14 @@
       <c r="T23" s="6"/>
     </row>
     <row r="24" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="42"/>
+        <v>28</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="22"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
@@ -1619,14 +1618,14 @@
       <c r="T24" s="6"/>
     </row>
     <row r="25" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="42"/>
+        <v>29</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="22"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -1634,7 +1633,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
-      <c r="L25" s="42"/>
+      <c r="L25" s="22"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
@@ -1645,14 +1644,14 @@
       <c r="T25" s="6"/>
     </row>
     <row r="26" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="42"/>
+        <v>30</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="22"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -1671,14 +1670,14 @@
       <c r="T26" s="6"/>
     </row>
     <row r="27" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="42"/>
+        <v>31</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="22"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
@@ -1697,14 +1696,14 @@
       <c r="T27" s="6"/>
     </row>
     <row r="28" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="42"/>
+        <v>32</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="22"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
@@ -1723,16 +1722,16 @@
       <c r="T28" s="6"/>
     </row>
     <row r="29" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="42"/>
+      <c r="C29" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="22"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -1751,14 +1750,14 @@
       <c r="T29" s="6"/>
     </row>
     <row r="30" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="42"/>
+        <v>59</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="22"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -1777,14 +1776,14 @@
       <c r="T30" s="6"/>
     </row>
     <row r="31" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="42"/>
+        <v>58</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="22"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -1803,14 +1802,14 @@
       <c r="T31" s="6"/>
     </row>
     <row r="32" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="42"/>
+        <v>35</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="22"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -1829,16 +1828,16 @@
       <c r="T32" s="6"/>
     </row>
     <row r="33" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="23" t="s">
-        <v>39</v>
+      <c r="A33" s="25" t="s">
+        <v>36</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="42"/>
+        <v>60</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="22"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -1857,14 +1856,14 @@
       <c r="T33" s="6"/>
     </row>
     <row r="34" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="42"/>
+        <v>37</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="22"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -1883,14 +1882,14 @@
       <c r="T34" s="6"/>
     </row>
     <row r="35" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
+      <c r="A35" s="26"/>
       <c r="B35" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="42"/>
+        <v>38</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="22"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -1909,22 +1908,22 @@
       <c r="T35" s="6"/>
     </row>
     <row r="36" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
-        <v>52</v>
+      <c r="A36" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>59</v>
+        <v>50</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="D36" s="12"/>
-      <c r="E36" s="42"/>
+      <c r="E36" s="22"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
-      <c r="J36" s="42"/>
+      <c r="J36" s="22"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
@@ -1937,14 +1936,14 @@
       <c r="T36" s="6"/>
     </row>
     <row r="37" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="22"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="42"/>
+        <v>54</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="22"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -1963,14 +1962,14 @@
       <c r="T37" s="6"/>
     </row>
     <row r="38" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="22"/>
+      <c r="A38" s="24"/>
       <c r="B38" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="42"/>
+        <v>53</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="22"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -1990,15 +1989,15 @@
     </row>
     <row r="39" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="42"/>
+        <v>39</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="22"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -2018,10 +2017,10 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.3">
@@ -2042,6 +2041,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="T2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A13"/>
     <mergeCell ref="A36:A38"/>
     <mergeCell ref="A33:A35"/>
     <mergeCell ref="L2:O2"/>
@@ -2053,11 +2057,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="T2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="50" orientation="portrait" r:id="rId1"/>
